--- a/Doc/Tests.xlsx
+++ b/Doc/Tests.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduetatfr-my.sharepoint.com/personal/lucielle_voeffray_studentfr_ch/Documents/EMF/Dossier de formation/5-Modules/VR3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="42" documentId="8_{59F13D17-64E5-4E38-A9FB-1F147C503149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A833FD-ABE9-4AB0-AB07-92B98464D284}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{75D06CE7-B0B4-415C-BED4-B8DB472F5E56}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{75D06CE7-B0B4-415C-BED4-B8DB472F5E56}"/>
   </bookViews>
   <sheets>
     <sheet name="Réseau" sheetId="1" r:id="rId1"/>
@@ -245,34 +245,34 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill>
@@ -318,20 +318,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -347,6 +333,13 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -688,16 +681,16 @@
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -705,23 +698,23 @@
       <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="7" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="8"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -732,11 +725,11 @@
     <mergeCell ref="D3:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
     <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+      <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -753,16 +746,16 @@
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -770,23 +763,23 @@
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="7" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="8"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -797,10 +790,10 @@
     <mergeCell ref="D3:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -818,16 +811,16 @@
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -835,23 +828,23 @@
       <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="7" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="8"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -883,16 +876,16 @@
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -900,23 +893,23 @@
       <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="7" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="8"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -948,16 +941,16 @@
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -965,23 +958,23 @@
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="7" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="8"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Doc/Tests.xlsx
+++ b/Doc/Tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{59F13D17-64E5-4E38-A9FB-1F147C503149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A833FD-ABE9-4AB0-AB07-92B98464D284}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F157D24-6626-4F2E-B1E4-C93E8DCD21B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{75D06CE7-B0B4-415C-BED4-B8DB472F5E56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{75D06CE7-B0B4-415C-BED4-B8DB472F5E56}"/>
   </bookViews>
   <sheets>
     <sheet name="Réseau" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="46">
   <si>
     <t>Test N</t>
   </si>
@@ -72,15 +72,128 @@
     <t>PT</t>
   </si>
   <si>
-    <t>ST</t>
+    <t>net-01</t>
+  </si>
+  <si>
+    <t>net-02</t>
+  </si>
+  <si>
+    <t>net-03</t>
+  </si>
+  <si>
+    <t>net-04</t>
+  </si>
+  <si>
+    <t>pve-01</t>
+  </si>
+  <si>
+    <t>pve-02</t>
+  </si>
+  <si>
+    <t>sto-01</t>
+  </si>
+  <si>
+    <t>sto-02</t>
+  </si>
+  <si>
+    <t>sto-03</t>
+  </si>
+  <si>
+    <t>Le disque est créé sans erreur</t>
+  </si>
+  <si>
+    <t>sto-04</t>
+  </si>
+  <si>
+    <t>sto-05</t>
+  </si>
+  <si>
+    <t>tpl-01</t>
+  </si>
+  <si>
+    <t>ans-01</t>
+  </si>
+  <si>
+    <t>Vérifier que chaque nœud est accessible depuis le management</t>
+  </si>
+  <si>
+    <t>L’interface web est accessible sur les trois nœuds</t>
+  </si>
+  <si>
+    <t>Les VMs sont capables de ping le server 9.9.9.9</t>
+  </si>
+  <si>
+    <t>Contrôler que les VMs n'ont pas accès au réseau de management</t>
+  </si>
+  <si>
+    <t>le ping du cluster (10.19.59.10) ne répond rien</t>
+  </si>
+  <si>
+    <t>Contrôler que les VMs n'ont pas accès au stockage</t>
+  </si>
+  <si>
+    <t>Le ping du réseau stockage (10.19.58.11) ne répond rien</t>
+  </si>
+  <si>
+    <t>Contrôler que les nodes sont gérable depuis une seule interface web</t>
+  </si>
+  <si>
+    <t>Dans l'interface web (10.19.59.11:8006), les trois nœuds sont visibles</t>
+  </si>
+  <si>
+    <t>Les nœuds sont nommés selon les standards d'entreprise</t>
+  </si>
+  <si>
+    <t>Les nœuds sont nommés selon les stanbdards d'entreprise: A41-srv-XX</t>
+  </si>
+  <si>
+    <t>Vérifier que le stockage est visible sur les 3 nœuds</t>
+  </si>
+  <si>
+    <t>Le stockage est visible sur les 3 nœuds</t>
+  </si>
+  <si>
+    <t>Créer un disque de test sur le stockage depuis le nœud 01</t>
+  </si>
+  <si>
+    <t>Créer un disque de test sur le stockage depuis le nœud 02</t>
+  </si>
+  <si>
+    <t>Créer un disque de test sur le stockage depuis le nœud 03</t>
+  </si>
+  <si>
+    <t>Vérifier l'état de santé de Ceph</t>
+  </si>
+  <si>
+    <t>L'état de santé de CEPH est sain</t>
+  </si>
+  <si>
+    <t>La VM windows Server démarrent bien</t>
+  </si>
+  <si>
+    <t>La VM peut démarrer depuis un templates, l'IP attribuée est la bonne selon Ansible et le nom de la machine en interne est correct aussi</t>
+  </si>
+  <si>
+    <t>vérifier que Ansible est capable de créer une VM et de la détruire, selon les tags qui lui sont attribués</t>
+  </si>
+  <si>
+    <t>La VM est créée selon les spécifications de Ansible</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -96,7 +209,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -239,11 +352,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -268,11 +390,209 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -725,10 +1045,10 @@
     <mergeCell ref="D3:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -790,10 +1110,10 @@
     <mergeCell ref="D3:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -855,10 +1175,10 @@
     <mergeCell ref="D3:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -920,10 +1240,10 @@
     <mergeCell ref="D3:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -933,58 +1253,734 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B923459-2D07-425B-99C6-98F8800FFEA6}">
-  <dimension ref="B1:E5"/>
+  <dimension ref="B1:E70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="12" max="13" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="B3" s="6"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="4"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="18" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="11"/>
+      <c r="D5" s="13"/>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
+    <row r="6" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="6"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="7"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="6"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="7"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="6"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="7"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="6"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="7"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="6"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="7"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="5"/>
+    </row>
+    <row r="31" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="6"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="7"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="5"/>
+    </row>
+    <row r="36" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="B38" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="6"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="7"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B43" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="8"/>
+      <c r="D43" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="6"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="7"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="5"/>
+    </row>
+    <row r="46" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B47" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="8"/>
+      <c r="D48" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="6"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="7"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="5"/>
+    </row>
+    <row r="51" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B53" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="6"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="7"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="5"/>
+    </row>
+    <row r="56" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="8"/>
+      <c r="D58" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="6"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="7"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="5"/>
+    </row>
+    <row r="61" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="B63" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="8"/>
+      <c r="D63" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="6"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="7"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="5"/>
+    </row>
+    <row r="66" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B67" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="8"/>
+      <c r="D68" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B69" s="6"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="7"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="42">
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="D58:D60"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
   </mergeCells>
-  <conditionalFormatting sqref="E3 E5">
+  <conditionalFormatting sqref="E5">
+    <cfRule type="cellIs" dxfId="27" priority="27" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="28" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="cellIs" dxfId="25" priority="25" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="26" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15">
+    <cfRule type="cellIs" dxfId="23" priority="23" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="24" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25">
+    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30">
+    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E35">
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E40">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E45">
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E50">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E55">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E65">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E70">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>

--- a/Doc/Tests.xlsx
+++ b/Doc/Tests.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F157D24-6626-4F2E-B1E4-C93E8DCD21B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{75D06CE7-B0B4-415C-BED4-B8DB472F5E56}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{75D06CE7-B0B4-415C-BED4-B8DB472F5E56}"/>
   </bookViews>
   <sheets>
     <sheet name="Réseau" sheetId="1" r:id="rId1"/>
@@ -372,6 +372,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -385,26 +395,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1015,25 +1015,25 @@
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="10"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="6"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
@@ -1080,25 +1080,25 @@
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="10"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="6"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
@@ -1145,25 +1145,25 @@
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="10"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="6"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
@@ -1210,25 +1210,25 @@
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="10"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="6"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="19"/>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
@@ -1263,576 +1263,609 @@
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="6"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="14"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="6"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="18" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="17"/>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="12" t="s">
+      <c r="C8" s="14"/>
+      <c r="D8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="6"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="18" t="s">
+      <c r="B9" s="12"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="17"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="14"/>
+      <c r="D13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="18" t="s">
+      <c r="B14" s="12"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="7"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="17"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="12" t="s">
+      <c r="C18" s="14"/>
+      <c r="D18" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="18" t="s">
+      <c r="B19" s="12"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="7"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="17"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="12" t="s">
+      <c r="C23" s="14"/>
+      <c r="D23" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="18" t="s">
+      <c r="B24" s="12"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="7"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="17"/>
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="12" t="s">
+      <c r="C28" s="14"/>
+      <c r="D28" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="6"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="18" t="s">
+      <c r="B29" s="12"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="7"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="17"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="2:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="12" t="s">
+      <c r="C33" s="14"/>
+      <c r="D33" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="6"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="18" t="s">
+      <c r="B34" s="12"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="7"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="17"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="12" t="s">
+      <c r="C38" s="14"/>
+      <c r="D38" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="6"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="18" t="s">
+      <c r="B39" s="12"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="7"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="17"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="12" t="s">
+      <c r="C43" s="14"/>
+      <c r="D43" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="6"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="18" t="s">
+      <c r="B44" s="12"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="45" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="7"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="13"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="17"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="48" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="12" t="s">
+      <c r="C48" s="14"/>
+      <c r="D48" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="6"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="18" t="s">
+      <c r="B49" s="12"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="7"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="17"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="53" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C53" s="8"/>
-      <c r="D53" s="12" t="s">
+      <c r="C53" s="14"/>
+      <c r="D53" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="6"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="18" t="s">
+      <c r="B54" s="12"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="55" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="7"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="13"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="17"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D57" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="58" spans="2:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="12" t="s">
+      <c r="C58" s="14"/>
+      <c r="D58" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="6"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="18" t="s">
+      <c r="B59" s="12"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="60" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="7"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="13"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="17"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D62" s="16" t="s">
+      <c r="D62" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="63" spans="2:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C63" s="8"/>
-      <c r="D63" s="12" t="s">
+      <c r="C63" s="14"/>
+      <c r="D63" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E63" s="6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B64" s="6"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="18" t="s">
+      <c r="B64" s="12"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="7"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="13"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="17"/>
       <c r="E65" s="5"/>
     </row>
     <row r="66" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D67" s="16" t="s">
+      <c r="D67" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="68" spans="2:5" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C68" s="8"/>
-      <c r="D68" s="12" t="s">
+      <c r="C68" s="14"/>
+      <c r="D68" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E68" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B69" s="6"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="18" t="s">
+      <c r="B69" s="12"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="70" spans="2:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="7"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="13"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="17"/>
       <c r="E70" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="D53:D55"/>
     <mergeCell ref="B68:B70"/>
     <mergeCell ref="C68:C70"/>
     <mergeCell ref="D68:D70"/>
@@ -1842,39 +1875,6 @@
     <mergeCell ref="B63:B65"/>
     <mergeCell ref="C63:C65"/>
     <mergeCell ref="D63:D65"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="D48:D50"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="D53:D55"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
   </mergeCells>
   <conditionalFormatting sqref="E5">
     <cfRule type="cellIs" dxfId="27" priority="27" operator="equal">

--- a/Doc/Tests.xlsx
+++ b/Doc/Tests.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12586699-8257-4957-B320-F0D4434FFEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F376A9-1DDA-423A-ACA2-416C636DA77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{75D06CE7-B0B4-415C-BED4-B8DB472F5E56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75D06CE7-B0B4-415C-BED4-B8DB472F5E56}"/>
   </bookViews>
   <sheets>
     <sheet name="Réseau" sheetId="1" r:id="rId1"/>
     <sheet name="Ansible" sheetId="2" r:id="rId2"/>
     <sheet name="VMs" sheetId="3" r:id="rId3"/>
     <sheet name="Proxmox" sheetId="4" r:id="rId4"/>
-    <sheet name="Modèles-VMs" sheetId="5" r:id="rId5"/>
+    <sheet name="HA" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="73">
   <si>
     <t>Test N</t>
   </si>
@@ -214,13 +214,58 @@
   </si>
   <si>
     <t>ans-XX</t>
+  </si>
+  <si>
+    <t>Vérifier que les bridges n'aient que les VLANs 280-282 et pas les valeurs par défaut</t>
+  </si>
+  <si>
+    <t>Les bridges vmbr0 ont 280-282 et les vmbr1 ne sont pas VLAN aware</t>
+  </si>
+  <si>
+    <t>net-05</t>
+  </si>
+  <si>
+    <t>pve-03</t>
+  </si>
+  <si>
+    <t>Le quorum Proxmox est sain</t>
+  </si>
+  <si>
+    <t>3 votes, quorum à 2</t>
+  </si>
+  <si>
+    <t>ha-01</t>
+  </si>
+  <si>
+    <t>ha-02</t>
+  </si>
+  <si>
+    <t>ha-03</t>
+  </si>
+  <si>
+    <t>Vérifier que les services HA de Proxmox sont actifs sur les nœuds.</t>
+  </si>
+  <si>
+    <t>Migrer volontairement une VM HA vers un autre nœud.</t>
+  </si>
+  <si>
+    <t>La VM est déplacée sur le nœud cible sans erreur.</t>
+  </si>
+  <si>
+    <t>Quorum ok + les trois nœuds s'affichent, 1 master et 2 idle + Les VMs affichent léeurs présences dans le HA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panne d'un nœud / Eteindre un nœud avec un VM </t>
+  </si>
+  <si>
+    <t>La VM est recréée sur un des autres nœuds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +281,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -245,7 +295,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -388,11 +438,85 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -408,11 +532,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -421,39 +562,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="81">
+  <dxfs count="88">
     <dxf>
       <fill>
         <patternFill>
@@ -492,6 +663,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -548,6 +726,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -562,6 +747,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -576,6 +768,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -590,6 +789,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -604,6 +810,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -618,6 +831,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -632,6 +852,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -646,6 +873,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -660,6 +894,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -667,7 +908,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -716,6 +957,48 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -737,6 +1020,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -765,6 +1055,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -779,6 +1076,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -821,6 +1125,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -835,112 +1146,21 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1358,15 +1578,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D454C39-7E38-45B8-8E96-C5C0065B9133}">
-  <dimension ref="B1:F26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:F31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:6">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1376,36 +1597,46 @@
       <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="11" t="s">
+      <c r="F2" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="B3" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="11"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="4" t="s">
+      <c r="C3" s="20"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="24"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="26" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="12"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="30.75" thickBot="1">
+      <c r="B5" s="25"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="8" spans="2:6">
       <c r="B8" s="6" t="s">
         <v>0</v>
       </c>
@@ -1418,51 +1649,51 @@
       <c r="E8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
+    <row r="9" spans="2:6" ht="60">
+      <c r="B9" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="15">
         <v>46171</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="23"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="20" t="s">
+    <row r="10" spans="2:6">
+      <c r="B10" s="18"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="24"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+    <row r="11" spans="2:6" ht="60.75" thickBot="1">
+      <c r="B11" s="19"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
       <c r="E11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="13" spans="2:6">
       <c r="B13" s="6" t="s">
         <v>0</v>
       </c>
@@ -1475,51 +1706,51 @@
       <c r="E13" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
+    <row r="14" spans="2:6" ht="60">
+      <c r="B14" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="15">
         <v>46171</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="23"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="20" t="s">
+    <row r="15" spans="2:6">
+      <c r="B15" s="18"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="24"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
+    <row r="16" spans="2:6" ht="60.75" thickBot="1">
+      <c r="B16" s="19"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
       <c r="E16" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="18" spans="2:6">
       <c r="B18" s="6" t="s">
         <v>0</v>
       </c>
@@ -1532,51 +1763,51 @@
       <c r="E18" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="B19" s="23" t="s">
+    <row r="19" spans="2:6" ht="60">
+      <c r="B19" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="15">
         <v>46171</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="23"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="20" t="s">
+    <row r="20" spans="2:6">
+      <c r="B20" s="18"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="24"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
+    <row r="21" spans="2:6" ht="60.75" thickBot="1">
+      <c r="B21" s="19"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
       <c r="E21" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="23" spans="2:6">
       <c r="B23" s="6" t="s">
         <v>0</v>
       </c>
@@ -1589,57 +1820,111 @@
       <c r="E23" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="B24" s="23" t="s">
+    <row r="24" spans="2:6" ht="60">
+      <c r="B24" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="15">
         <v>46171</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="16" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="F24" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="23"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="20" t="s">
+    <row r="25" spans="2:6">
+      <c r="B25" s="18"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="24"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
+    <row r="26" spans="2:6" ht="60.75" thickBot="1">
+      <c r="B26" s="19"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
       <c r="E26" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="14" t="s">
         <v>40</v>
       </c>
     </row>
+    <row r="27" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="28" spans="2:6">
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="80.25" customHeight="1">
+      <c r="B29" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="28">
+        <v>46174</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="24"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" ht="77.25" customHeight="1" thickBot="1">
+      <c r="B31" s="25"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
+  <mergeCells count="18">
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
@@ -1649,49 +1934,89 @@
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D9:D11"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="80" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="18" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="19" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9 F14 F19 F24">
-    <cfRule type="cellIs" dxfId="78" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="17" operator="equal">
       <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="77" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="15" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="16" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="cellIs" dxfId="75" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="13" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="14" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="cellIs" dxfId="73" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="11" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="12" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="9" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="10" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="cellIs" dxfId="76" priority="8" operator="equal">
+      <formula>"~"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="cellIs" dxfId="75" priority="6" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="7" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29 E31">
+    <cfRule type="cellIs" dxfId="73" priority="4" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="5" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
+    <cfRule type="cellIs" dxfId="71" priority="3" operator="equal">
+      <formula>"~"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
+    <cfRule type="cellIs" dxfId="70" priority="1" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1702,15 +2027,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53F42EDC-2756-4AFE-B2C2-43F293949C99}">
   <dimension ref="B1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:6">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1724,32 +2049,32 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="11" t="s">
+    <row r="3" spans="2:6">
+      <c r="B3" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="11"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="17"/>
+    <row r="4" spans="2:6">
+      <c r="B4" s="24"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="12"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="18"/>
+    <row r="5" spans="2:6" ht="15.75" thickBot="1">
+      <c r="B5" s="25"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="8" spans="2:6">
       <c r="B8" s="6" t="s">
         <v>0</v>
       </c>
@@ -1762,49 +2087,49 @@
       <c r="E8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
+    <row r="9" spans="2:6" ht="75">
+      <c r="B9" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="15">
         <v>46171</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="23"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="20" t="s">
+    <row r="10" spans="2:6">
+      <c r="B10" s="18"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="24"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+    <row r="11" spans="2:6" ht="75.75" thickBot="1">
+      <c r="B11" s="19"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
       <c r="E11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="22"/>
-    </row>
-    <row r="12" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F11" s="14"/>
+    </row>
+    <row r="12" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="13" spans="2:6">
       <c r="B13" s="6" t="s">
         <v>0</v>
       </c>
@@ -1817,46 +2142,46 @@
       <c r="E13" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
+    <row r="14" spans="2:6" ht="90">
+      <c r="B14" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="15">
         <v>46171</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>48</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="23"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="20" t="s">
+    <row r="15" spans="2:6">
+      <c r="B15" s="18"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="24"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
+    <row r="16" spans="2:6" ht="90.75" thickBot="1">
+      <c r="B16" s="19"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
       <c r="E16" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="22"/>
+      <c r="F16" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1871,16 +2196,11 @@
     <mergeCell ref="D9:D11"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="69" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="7" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="8" operator="equal">
       <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="67" priority="6" operator="equal">
-      <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
@@ -1890,9 +2210,7 @@
     <cfRule type="cellIs" dxfId="65" priority="5" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="cellIs" dxfId="64" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="6" operator="equal">
       <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1902,6 +2220,9 @@
     </cfRule>
     <cfRule type="cellIs" dxfId="62" priority="2" operator="equal">
       <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="3" operator="equal">
+      <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1911,15 +2232,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4790C484-E1F4-477D-8FA1-71B8C3FD175C}">
   <dimension ref="B1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:6">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1933,32 +2254,32 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="11" t="s">
+    <row r="3" spans="2:6">
+      <c r="B3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="17"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="11"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="17"/>
+    <row r="4" spans="2:6">
+      <c r="B4" s="24"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="12"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="18"/>
+    <row r="5" spans="2:6" ht="15.75" thickBot="1">
+      <c r="B5" s="25"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="8" spans="2:6">
       <c r="B8" s="6" t="s">
         <v>0</v>
       </c>
@@ -1971,46 +2292,46 @@
       <c r="E8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="165" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
+    <row r="9" spans="2:6" ht="150">
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="15">
         <v>46171</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="23"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="20" t="s">
+    <row r="10" spans="2:6">
+      <c r="B10" s="18"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="24"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+    <row r="11" spans="2:6" ht="150.75" thickBot="1">
+      <c r="B11" s="19"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
       <c r="E11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="14" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2024,16 +2345,11 @@
     <mergeCell ref="D9:D11"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="61" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="4" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
       <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
-      <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
@@ -2042,6 +2358,9 @@
     </cfRule>
     <cfRule type="cellIs" dxfId="57" priority="2" operator="equal">
       <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="3" operator="equal">
+      <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2050,54 +2369,65 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57A037A-7FB6-43DC-9807-B03536B9059D}">
-  <dimension ref="B1:F40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:F45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:6">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="23" t="s">
+      <c r="F2" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="15" customHeight="1">
+      <c r="B3" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="23"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="4" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="18"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="24"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="30.75" thickBot="1">
+      <c r="B5" s="19"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="7" spans="2:6">
       <c r="B7" s="6" t="s">
         <v>0</v>
       </c>
@@ -2110,51 +2440,51 @@
       <c r="E7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
+    <row r="8" spans="2:6" ht="90">
+      <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="15">
         <v>46171</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="16" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="23"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="20" t="s">
+    <row r="9" spans="2:6">
+      <c r="B9" s="18"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="24"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+    <row r="10" spans="2:6" ht="90.75" thickBot="1">
+      <c r="B10" s="19"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
       <c r="E10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="12" spans="2:6">
       <c r="B12" s="6" t="s">
         <v>0</v>
       </c>
@@ -2167,51 +2497,51 @@
       <c r="E12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="B13" s="23" t="s">
+    <row r="13" spans="2:6" ht="75">
+      <c r="B13" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="15">
         <v>46171</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="23"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="20" t="s">
+    <row r="14" spans="2:6">
+      <c r="B14" s="18"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="120.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="24"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
+    <row r="15" spans="2:6" ht="120.75" thickBot="1">
+      <c r="B15" s="19"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
       <c r="E15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="17" spans="2:6">
       <c r="B17" s="6" t="s">
         <v>0</v>
       </c>
@@ -2224,51 +2554,51 @@
       <c r="E17" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B18" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="25">
-        <v>46171</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>27</v>
+    <row r="18" spans="2:6" ht="45" customHeight="1">
+      <c r="B18" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="15">
+        <v>46174</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="23"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="20" t="s">
+    <row r="19" spans="2:6">
+      <c r="B19" s="18"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="24"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
+    <row r="20" spans="2:6" ht="42" customHeight="1" thickBot="1">
+      <c r="B20" s="19"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
       <c r="E20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="22" spans="2:6">
       <c r="B22" s="6" t="s">
         <v>0</v>
       </c>
@@ -2281,49 +2611,51 @@
       <c r="E22" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B23" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="25">
+    <row r="23" spans="2:6" ht="75">
+      <c r="B23" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="36">
         <v>46171</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>29</v>
+      <c r="D23" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="23"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="20" t="s">
+    <row r="24" spans="2:6">
+      <c r="B24" s="34"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="24"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
+    <row r="25" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B25" s="35"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="10"/>
       <c r="E25" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="22"/>
-    </row>
-    <row r="26" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="27" spans="2:6">
       <c r="B27" s="6" t="s">
         <v>0</v>
       </c>
@@ -2336,49 +2668,49 @@
       <c r="E27" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B28" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="25">
+    <row r="28" spans="2:6" ht="30" customHeight="1">
+      <c r="B28" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="36">
         <v>46171</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>30</v>
+      <c r="D28" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="F28" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="23"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="20" t="s">
+    <row r="29" spans="2:6" ht="45" customHeight="1">
+      <c r="B29" s="34"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="24"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
+    <row r="30" spans="2:6" ht="30.75" thickBot="1">
+      <c r="B30" s="35"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="10"/>
       <c r="E30" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F30" s="22"/>
-    </row>
-    <row r="31" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F30" s="14"/>
+    </row>
+    <row r="31" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="32" spans="2:6">
       <c r="B32" s="6" t="s">
         <v>0</v>
       </c>
@@ -2391,49 +2723,49 @@
       <c r="E32" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B33" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="25">
+    <row r="33" spans="2:6" ht="30" customHeight="1">
+      <c r="B33" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="36">
         <v>46171</v>
       </c>
-      <c r="D33" s="15" t="s">
-        <v>31</v>
+      <c r="D33" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="23"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="20" t="s">
+    <row r="34" spans="2:6" ht="30" customHeight="1">
+      <c r="B34" s="34"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="24"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
+    <row r="35" spans="2:6" ht="30.75" thickBot="1">
+      <c r="B35" s="35"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="10"/>
       <c r="E35" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F35" s="22"/>
-    </row>
-    <row r="36" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F35" s="14"/>
+    </row>
+    <row r="36" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="37" spans="2:6">
       <c r="B37" s="6" t="s">
         <v>0</v>
       </c>
@@ -2446,140 +2778,211 @@
       <c r="E37" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="2:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="B38" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="25">
+    <row r="38" spans="2:6" ht="30" customHeight="1">
+      <c r="B38" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="36">
         <v>46171</v>
       </c>
-      <c r="D38" s="15" t="s">
-        <v>32</v>
+      <c r="D38" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F38" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="23"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="20" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="34"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="2:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="24"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
+    <row r="40" spans="2:6" ht="30.75" thickBot="1">
+      <c r="B40" s="35"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="10"/>
       <c r="E40" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" s="14"/>
+    </row>
+    <row r="41" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="42" spans="2:6">
+      <c r="B42" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" ht="60">
+      <c r="B43" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="36">
+        <v>46171</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="22"/>
+      <c r="F43" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="34"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" ht="30.75" thickBot="1">
+      <c r="B45" s="35"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F45" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="22">
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B28:B30"/>
     <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="D13:D15"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D33:D35"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="C18:C20"/>
     <mergeCell ref="D18:D20"/>
     <mergeCell ref="B23:B25"/>
   </mergeCells>
-  <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="56" priority="16" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="17" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8 F13 F18 F23 F28 F33 F38">
-    <cfRule type="cellIs" dxfId="54" priority="15" operator="equal">
+  <conditionalFormatting sqref="F8 F13 F23 F28 F33 F38 F43">
+    <cfRule type="cellIs" dxfId="53" priority="27" operator="equal">
       <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="cellIs" dxfId="53" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="25" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="cellIs" dxfId="51" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="23" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="24" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="cellIs" dxfId="48" priority="21" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="22" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
+    <cfRule type="cellIs" dxfId="46" priority="19" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="20" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="cellIs" dxfId="44" priority="17" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="18" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F38">
+    <cfRule type="cellIs" dxfId="42" priority="15" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="16" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F43">
+    <cfRule type="cellIs" dxfId="40" priority="13" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="14" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="cellIs" dxfId="35" priority="9" operator="equal">
+      <formula>"~"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="cellIs" dxfId="34" priority="7" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="8" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="cellIs" dxfId="49" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
+      <formula>"~"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="10" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="cellIs" dxfId="47" priority="7" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="8" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="cellIs" dxfId="45" priority="5" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="6" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
-    <cfRule type="cellIs" dxfId="43" priority="3" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="4" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F38">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2590,7 +2993,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B923459-2D07-425B-99C6-98F8800FFEA6}">
   <dimension ref="B1:F73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="18.85546875" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
@@ -2598,8 +3001,8 @@
     <col min="12" max="13" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:6">
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
@@ -2612,63 +3015,341 @@
       <c r="E2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="23"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+    <row r="3" spans="2:6">
+      <c r="B3" s="18"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
       <c r="E3" s="9"/>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="23"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="20" t="s">
+    <row r="4" spans="2:6">
+      <c r="B4" s="18"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="24"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
+    <row r="5" spans="2:6" ht="15.75" thickBot="1">
+      <c r="B5" s="19"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="22"/>
-    </row>
-    <row r="8" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:6" ht="48" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="46.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="F5" s="14"/>
+    </row>
+    <row r="6" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="7" spans="2:6">
+      <c r="B7" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="105">
+      <c r="B8" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="15">
+        <v>46174</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="18"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="105.75" thickBot="1">
+      <c r="B10" s="19"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="12" spans="2:6">
+      <c r="B12" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B13" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="15">
+        <v>46174</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="18"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B15" s="19"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" spans="2:6" ht="15.75" thickBot="1"/>
+    <row r="17" spans="2:6">
+      <c r="B17" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B18" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="15">
+        <v>46174</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="18"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="45.75" thickBot="1">
+      <c r="B20" s="19"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="14"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="42"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="42"/>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="42"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="42"/>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="42"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="42"/>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="42"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="42"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="42"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="42"/>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="42"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="42"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="42"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="42"/>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="42"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="42"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="42"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="42"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="42"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+    </row>
+    <row r="43" spans="2:6" ht="30" customHeight="1"/>
+    <row r="48" spans="2:6" ht="30" customHeight="1"/>
+    <row r="53" ht="30" customHeight="1"/>
+    <row r="68" ht="75" customHeight="1"/>
+    <row r="73" ht="75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="12">
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
   </mergeCells>
   <conditionalFormatting sqref="F3">
-    <cfRule type="cellIs" dxfId="39" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="76" operator="equal">
+      <formula>"~"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="77" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="78" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="cellIs" dxfId="37" priority="55" operator="equal">
+  <conditionalFormatting sqref="F18">
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
       <formula>"~"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+      <formula>"~"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"~"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Doc/Tests.xlsx
+++ b/Doc/Tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F376A9-1DDA-423A-ACA2-416C636DA77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24A602B-B35A-42B9-8C26-50382D99A0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75D06CE7-B0B4-415C-BED4-B8DB472F5E56}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="4" xr2:uid="{75D06CE7-B0B4-415C-BED4-B8DB472F5E56}"/>
   </bookViews>
   <sheets>
     <sheet name="Réseau" sheetId="1" r:id="rId1"/>
@@ -516,7 +516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -540,20 +540,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -562,21 +576,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -584,11 +587,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -608,23 +620,20 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="88">
+  <dxfs count="65">
     <dxf>
       <fill>
         <patternFill>
@@ -726,6 +735,62 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -747,6 +812,34 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -754,6 +847,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -789,6 +889,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -831,6 +945,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -845,6 +973,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -852,6 +994,34 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -859,6 +1029,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -873,13 +1050,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -894,13 +1064,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -909,321 +1072,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1605,21 +1453,21 @@
       </c>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="15"/>
       <c r="F3" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="24"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="26" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="15" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="8" t="s">
@@ -1627,10 +1475,10 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="30.75" thickBot="1">
-      <c r="B5" s="25"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="27"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="14" t="s">
         <v>40</v>
       </c>
@@ -1654,13 +1502,13 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="60">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="34">
         <v>46171</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="28" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="9" t="s">
@@ -1671,9 +1519,9 @@
       </c>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="18"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="12" t="s">
         <v>4</v>
       </c>
@@ -1682,9 +1530,9 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="60.75" thickBot="1">
-      <c r="B11" s="19"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
       <c r="E11" s="10" t="s">
         <v>38</v>
       </c>
@@ -1711,13 +1559,13 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="60">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="34">
         <v>46171</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="28" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="9" t="s">
@@ -1728,9 +1576,9 @@
       </c>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="18"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
       <c r="E15" s="12" t="s">
         <v>4</v>
       </c>
@@ -1739,9 +1587,9 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="60.75" thickBot="1">
-      <c r="B16" s="19"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
       <c r="E16" s="10" t="s">
         <v>21</v>
       </c>
@@ -1768,13 +1616,13 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="60">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="34">
         <v>46171</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="28" t="s">
         <v>22</v>
       </c>
       <c r="E19" s="9" t="s">
@@ -1785,9 +1633,9 @@
       </c>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="18"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="12" t="s">
         <v>4</v>
       </c>
@@ -1796,9 +1644,9 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="60.75" thickBot="1">
-      <c r="B21" s="19"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
       <c r="E21" s="10" t="s">
         <v>41</v>
       </c>
@@ -1825,13 +1673,13 @@
       </c>
     </row>
     <row r="24" spans="2:6" ht="60">
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="34">
         <v>46171</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="28" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="9" t="s">
@@ -1842,9 +1690,9 @@
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="18"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
       <c r="E25" s="12" t="s">
         <v>4</v>
       </c>
@@ -1853,9 +1701,9 @@
       </c>
     </row>
     <row r="26" spans="2:6" ht="60.75" thickBot="1">
-      <c r="B26" s="19"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
       <c r="E26" s="10" t="s">
         <v>42</v>
       </c>
@@ -1882,16 +1730,16 @@
       </c>
     </row>
     <row r="29" spans="2:6" ht="80.25" customHeight="1">
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="25">
         <v>46174</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="E29" s="31" t="s">
+      <c r="E29" s="17" t="s">
         <v>59</v>
       </c>
       <c r="F29" s="13" t="s">
@@ -1899,10 +1747,10 @@
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="24"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="26" t="s">
+      <c r="B30" s="23"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="15" t="s">
         <v>4</v>
       </c>
       <c r="F30" s="8" t="s">
@@ -1910,10 +1758,10 @@
       </c>
     </row>
     <row r="31" spans="2:6" ht="77.25" customHeight="1" thickBot="1">
-      <c r="B31" s="25"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="32" t="s">
+      <c r="B31" s="24"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="18" t="s">
         <v>59</v>
       </c>
       <c r="F31" s="14" t="s">
@@ -1922,6 +1770,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="C29:C31"/>
     <mergeCell ref="D29:D31"/>
@@ -1938,86 +1788,84 @@
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
   </mergeCells>
-  <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="87" priority="18" operator="equal">
+  <conditionalFormatting sqref="E5">
+    <cfRule type="cellIs" dxfId="64" priority="18" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="19" operator="equal">
       <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31">
+    <cfRule type="cellIs" dxfId="62" priority="4" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="5" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:F3">
+    <cfRule type="cellIs" dxfId="60" priority="6" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29:F29">
+    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="2" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="cellIs" dxfId="56" priority="8" operator="equal">
+      <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9 F14 F19 F24">
-    <cfRule type="cellIs" dxfId="85" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="17" operator="equal">
       <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="84" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="15" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="16" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="cellIs" dxfId="82" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="13" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="14" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="cellIs" dxfId="80" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="11" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="12" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="cellIs" dxfId="78" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="9" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="10" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="cellIs" dxfId="76" priority="8" operator="equal">
-      <formula>"~"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="cellIs" dxfId="75" priority="6" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="7" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E29 E31">
-    <cfRule type="cellIs" dxfId="73" priority="4" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="10" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29">
-    <cfRule type="cellIs" dxfId="71" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="3" operator="equal">
       <formula>"~"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
-    <cfRule type="cellIs" dxfId="70" priority="1" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="2" operator="equal">
-      <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2050,25 +1898,25 @@
       </c>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="35"/>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="24"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="22"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="35"/>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B5" s="25"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="23"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
@@ -2092,13 +1940,13 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="75">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="34">
         <v>46171</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="28" t="s">
         <v>52</v>
       </c>
       <c r="E9" s="9" t="s">
@@ -2109,9 +1957,9 @@
       </c>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="18"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="12" t="s">
         <v>4</v>
       </c>
@@ -2120,9 +1968,9 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="75.75" thickBot="1">
-      <c r="B11" s="19"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
       <c r="E11" s="10" t="s">
         <v>49</v>
       </c>
@@ -2147,13 +1995,13 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="90">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="34">
         <v>46171</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="28" t="s">
         <v>48</v>
       </c>
       <c r="E14" s="9" t="s">
@@ -2164,9 +2012,9 @@
       </c>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="18"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
       <c r="E15" s="12" t="s">
         <v>4</v>
       </c>
@@ -2175,9 +2023,9 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="90.75" thickBot="1">
-      <c r="B16" s="19"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
       <c r="E16" s="10" t="s">
         <v>50</v>
       </c>
@@ -2196,32 +2044,32 @@
     <mergeCell ref="D9:D11"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="68" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="7" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="8" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="66" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="4" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="5" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="6" operator="equal">
       <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="1" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="3" operator="equal">
       <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2255,25 +2103,25 @@
       </c>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="35"/>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="24"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="22"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="35"/>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B5" s="25"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="23"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
@@ -2297,13 +2145,13 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="150">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="34">
         <v>46171</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="28" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="9" t="s">
@@ -2314,9 +2162,9 @@
       </c>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="18"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
       <c r="E10" s="12" t="s">
         <v>4</v>
       </c>
@@ -2325,9 +2173,9 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="150.75" thickBot="1">
-      <c r="B11" s="19"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
       <c r="E11" s="10" t="s">
         <v>45</v>
       </c>
@@ -2345,21 +2193,21 @@
     <mergeCell ref="D9:D11"/>
   </mergeCells>
   <conditionalFormatting sqref="E3 E5">
-    <cfRule type="cellIs" dxfId="60" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="4" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="5" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="1" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
       <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2396,20 +2244,20 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="28"/>
       <c r="E3" s="9"/>
       <c r="F3" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="18"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
       <c r="E4" s="12" t="s">
         <v>4</v>
       </c>
@@ -2418,9 +2266,9 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="30.75" thickBot="1">
-      <c r="B5" s="19"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
       <c r="E5" s="10"/>
       <c r="F5" s="14" t="s">
         <v>40</v>
@@ -2445,13 +2293,13 @@
       </c>
     </row>
     <row r="8" spans="2:6" ht="90">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="34">
         <v>46171</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="28" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="9" t="s">
@@ -2462,9 +2310,9 @@
       </c>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="18"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="12" t="s">
         <v>4</v>
       </c>
@@ -2473,9 +2321,9 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="90.75" thickBot="1">
-      <c r="B10" s="19"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
       <c r="E10" s="10" t="s">
         <v>25</v>
       </c>
@@ -2502,13 +2350,13 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="75">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="34">
         <v>46171</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="28" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="9" t="s">
@@ -2519,9 +2367,9 @@
       </c>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="18"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
       <c r="E14" s="12" t="s">
         <v>4</v>
       </c>
@@ -2530,9 +2378,9 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="120.75" thickBot="1">
-      <c r="B15" s="19"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
       <c r="E15" s="10" t="s">
         <v>44</v>
       </c>
@@ -2559,13 +2407,13 @@
       </c>
     </row>
     <row r="18" spans="2:6" ht="45" customHeight="1">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="34">
         <v>46174</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="28" t="s">
         <v>62</v>
       </c>
       <c r="E18" s="9" t="s">
@@ -2576,9 +2424,9 @@
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="18"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
       <c r="E19" s="12" t="s">
         <v>4</v>
       </c>
@@ -2587,9 +2435,9 @@
       </c>
     </row>
     <row r="20" spans="2:6" ht="42" customHeight="1" thickBot="1">
-      <c r="B20" s="19"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
       <c r="E20" s="10" t="s">
         <v>63</v>
       </c>
@@ -2615,14 +2463,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="75">
-      <c r="B23" s="33" t="s">
+    <row r="23" spans="2:6" ht="75" customHeight="1">
+      <c r="B23" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="40">
         <v>46171</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="43" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="9" t="s">
@@ -2633,9 +2481,9 @@
       </c>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" s="34"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="44"/>
       <c r="E24" s="12" t="s">
         <v>4</v>
       </c>
@@ -2644,9 +2492,9 @@
       </c>
     </row>
     <row r="25" spans="2:6" ht="45.75" thickBot="1">
-      <c r="B25" s="35"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="10"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="45"/>
       <c r="E25" s="10" t="s">
         <v>28</v>
       </c>
@@ -2672,14 +2520,14 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="30" customHeight="1">
-      <c r="B28" s="33" t="s">
+    <row r="28" spans="2:6" ht="41.25" customHeight="1">
+      <c r="B28" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="36">
+      <c r="C28" s="40">
         <v>46171</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="43" t="s">
         <v>29</v>
       </c>
       <c r="E28" s="9" t="s">
@@ -2689,10 +2537,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="45" customHeight="1">
-      <c r="B29" s="34"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="9"/>
+    <row r="29" spans="2:6" ht="18.75" customHeight="1">
+      <c r="B29" s="38"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="44"/>
       <c r="E29" s="12" t="s">
         <v>4</v>
       </c>
@@ -2701,9 +2549,9 @@
       </c>
     </row>
     <row r="30" spans="2:6" ht="30.75" thickBot="1">
-      <c r="B30" s="35"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="10"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="45"/>
       <c r="E30" s="10" t="s">
         <v>14</v>
       </c>
@@ -2728,13 +2576,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="30" customHeight="1">
-      <c r="B33" s="33" t="s">
+      <c r="B33" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="40">
         <v>46171</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="43" t="s">
         <v>30</v>
       </c>
       <c r="E33" s="9" t="s">
@@ -2745,9 +2593,9 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="30" customHeight="1">
-      <c r="B34" s="34"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="44"/>
       <c r="E34" s="12" t="s">
         <v>4</v>
       </c>
@@ -2756,9 +2604,9 @@
       </c>
     </row>
     <row r="35" spans="2:6" ht="30.75" thickBot="1">
-      <c r="B35" s="35"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="10"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="45"/>
       <c r="E35" s="10" t="s">
         <v>14</v>
       </c>
@@ -2783,13 +2631,13 @@
       </c>
     </row>
     <row r="38" spans="2:6" ht="30" customHeight="1">
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="40">
         <v>46171</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="43" t="s">
         <v>31</v>
       </c>
       <c r="E38" s="9" t="s">
@@ -2800,9 +2648,9 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="34"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="44"/>
       <c r="E39" s="12" t="s">
         <v>4</v>
       </c>
@@ -2810,10 +2658,10 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="2:6" ht="30.75" thickBot="1">
-      <c r="B40" s="35"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="10"/>
+    <row r="40" spans="2:6" ht="52.5" customHeight="1" thickBot="1">
+      <c r="B40" s="39"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="45"/>
       <c r="E40" s="10" t="s">
         <v>14</v>
       </c>
@@ -2838,10 +2686,10 @@
       </c>
     </row>
     <row r="43" spans="2:6" ht="60">
-      <c r="B43" s="33" t="s">
+      <c r="B43" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="36">
+      <c r="C43" s="40">
         <v>46171</v>
       </c>
       <c r="D43" s="9" t="s">
@@ -2855,8 +2703,8 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="34"/>
-      <c r="C44" s="37"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="41"/>
       <c r="D44" s="9"/>
       <c r="E44" s="12" t="s">
         <v>4</v>
@@ -2866,8 +2714,8 @@
       </c>
     </row>
     <row r="45" spans="2:6" ht="30.75" thickBot="1">
-      <c r="B45" s="35"/>
-      <c r="C45" s="38"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="42"/>
       <c r="D45" s="10"/>
       <c r="E45" s="10" t="s">
         <v>33</v>
@@ -2875,7 +2723,23 @@
       <c r="F45" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="26">
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
     <mergeCell ref="B43:B45"/>
     <mergeCell ref="B38:B40"/>
     <mergeCell ref="B33:B35"/>
@@ -2885,104 +2749,88 @@
     <mergeCell ref="C33:C35"/>
     <mergeCell ref="C38:C40"/>
     <mergeCell ref="C43:C45"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
     <mergeCell ref="B23:B25"/>
   </mergeCells>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="cellIs" dxfId="32" priority="7" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="8" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="9" operator="equal">
+      <formula>"~"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F8 F13 F23 F28 F33 F38 F43">
-    <cfRule type="cellIs" dxfId="53" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="27" operator="equal">
       <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="cellIs" dxfId="52" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="25" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="26" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="cellIs" dxfId="50" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="23" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="24" operator="equal">
       <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="equal">
+      <formula>"~"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23">
-    <cfRule type="cellIs" dxfId="48" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="cellIs" dxfId="46" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33">
-    <cfRule type="cellIs" dxfId="44" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38">
-    <cfRule type="cellIs" dxfId="42" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43">
-    <cfRule type="cellIs" dxfId="40" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="14" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="cellIs" dxfId="35" priority="9" operator="equal">
-      <formula>"~"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="cellIs" dxfId="34" priority="7" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="8" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
-      <formula>"~"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3020,18 +2868,18 @@
       </c>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="18"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
       <c r="E3" s="9"/>
       <c r="F3" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="18"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
       <c r="E4" s="12" t="s">
         <v>4</v>
       </c>
@@ -3040,9 +2888,9 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B5" s="19"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
       <c r="E5" s="10"/>
       <c r="F5" s="14"/>
     </row>
@@ -3065,16 +2913,16 @@
       </c>
     </row>
     <row r="8" spans="2:6" ht="105">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="34">
         <v>46174</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="19" t="s">
         <v>70</v>
       </c>
       <c r="F8" s="13" t="s">
@@ -3082,9 +2930,9 @@
       </c>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="18"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
       <c r="E9" s="12" t="s">
         <v>4</v>
       </c>
@@ -3093,9 +2941,9 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="105.75" thickBot="1">
-      <c r="B10" s="19"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
       <c r="E10" s="10" t="s">
         <v>70</v>
       </c>
@@ -3120,16 +2968,16 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="34">
         <v>46174</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="19" t="s">
         <v>69</v>
       </c>
       <c r="F13" s="13" t="s">
@@ -3137,9 +2985,9 @@
       </c>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="18"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
       <c r="E14" s="12" t="s">
         <v>4</v>
       </c>
@@ -3148,9 +2996,9 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="45.75" thickBot="1">
-      <c r="B15" s="19"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
       <c r="E15" s="10" t="s">
         <v>69</v>
       </c>
@@ -3175,16 +3023,16 @@
       </c>
     </row>
     <row r="18" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="34">
         <v>46174</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="19" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="13" t="s">
@@ -3192,9 +3040,9 @@
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="18"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
       <c r="E19" s="12" t="s">
         <v>4</v>
       </c>
@@ -3203,90 +3051,90 @@
       </c>
     </row>
     <row r="20" spans="2:6" ht="45.75" thickBot="1">
-      <c r="B20" s="19"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
       <c r="E20" s="10" t="s">
         <v>72</v>
       </c>
       <c r="F20" s="14"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="42"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="42"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="22"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="42"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="42"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="22"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="B31" s="42"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="42"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="22"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="42"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="42"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="22"/>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="42"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="42"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="22"/>
     </row>
     <row r="34" spans="2:6">
-      <c r="B34" s="42"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="42"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="22"/>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="42"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="42"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="42"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="42"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="22"/>
     </row>
     <row r="37" spans="2:6">
-      <c r="B37" s="42"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="42"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="22"/>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="42"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
     </row>
     <row r="43" spans="2:6" ht="30" customHeight="1"/>
     <row r="48" spans="2:6" ht="30" customHeight="1"/>
@@ -3295,60 +3143,60 @@
     <row r="73" ht="75" customHeight="1"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="D13:D15"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="C18:C20"/>
     <mergeCell ref="D18:D20"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
   </mergeCells>
   <conditionalFormatting sqref="F3">
-    <cfRule type="cellIs" dxfId="26" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="76" operator="equal">
       <formula>"~"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="77" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="78" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"~"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"~"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"NOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"~"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
       <formula>"NOK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
-      <formula>"~"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"~"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"NOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
